--- a/Grades/Grades.xlsx
+++ b/Grades/Grades.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t xml:space="preserve">First name</t>
   </si>
@@ -49,6 +49,9 @@
     <t xml:space="preserve">Midterm 1</t>
   </si>
   <si>
+    <t xml:space="preserve">Final Project Proposal</t>
+  </si>
+  <si>
     <t xml:space="preserve">Luka</t>
   </si>
   <si>
@@ -65,6 +68,9 @@
   </si>
   <si>
     <t xml:space="preserve">khewett@poets.whittier.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">--</t>
   </si>
   <si>
     <t xml:space="preserve">Gary</t>
@@ -211,8 +217,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
-  <sheetFormatPr defaultColWidth="8.51953125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultColWidth="8.5234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.3"/>
@@ -220,6 +226,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="12.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17.95"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -255,16 +262,19 @@
       <c r="K2" s="0" t="s">
         <v>8</v>
       </c>
+      <c r="L2" s="0" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F3" s="0" t="n">
         <f aca="false">12.5/17</f>
@@ -276,6 +286,14 @@
       <c r="H3" s="0" t="n">
         <v>0</v>
       </c>
+      <c r="I3" s="0" t="n">
+        <f aca="false">1</f>
+        <v>1</v>
+      </c>
+      <c r="J3" s="0" t="n">
+        <f aca="false">28/30</f>
+        <v>0.933333333333333</v>
+      </c>
       <c r="K3" s="0" t="n">
         <f aca="false">21/30</f>
         <v>0.7</v>
@@ -283,13 +301,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F4" s="0" t="n">
         <f aca="false">16/17</f>
@@ -301,20 +319,48 @@
       <c r="H4" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="I4" s="0" t="n">
+        <f aca="false">1</f>
+        <v>1</v>
+      </c>
+      <c r="J4" s="0" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
       <c r="K4" s="0" t="n">
         <f aca="false">28.5/30</f>
         <v>0.95</v>
       </c>
     </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="H5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="J5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="0" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" s="0" t="n">
         <f aca="false">14/17</f>
@@ -326,6 +372,14 @@
       <c r="H6" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="I6" s="0" t="n">
+        <f aca="false">1</f>
+        <v>1</v>
+      </c>
+      <c r="J6" s="0" t="n">
+        <f aca="false">27/30</f>
+        <v>0.9</v>
+      </c>
       <c r="K6" s="0" t="n">
         <f aca="false">27/30</f>
         <v>0.9</v>
@@ -333,13 +387,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F7" s="0" t="n">
         <f aca="false">11/17</f>
@@ -351,6 +405,14 @@
       <c r="H7" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="I7" s="0" t="n">
+        <f aca="false">0.5</f>
+        <v>0.5</v>
+      </c>
+      <c r="J7" s="0" t="n">
+        <f aca="false">28/30</f>
+        <v>0.933333333333333</v>
+      </c>
       <c r="K7" s="0" t="n">
         <f aca="false">24/30</f>
         <v>0.8</v>
@@ -358,13 +420,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F8" s="0" t="n">
         <f aca="false">14/17</f>
@@ -376,6 +438,14 @@
       <c r="H8" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="I8" s="0" t="n">
+        <f aca="false">0.67</f>
+        <v>0.67</v>
+      </c>
+      <c r="J8" s="0" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
       <c r="K8" s="0" t="n">
         <f aca="false">25.5/30</f>
         <v>0.85</v>
@@ -383,13 +453,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F9" s="0" t="n">
         <f aca="false">15/17</f>
@@ -401,6 +471,14 @@
       <c r="H9" s="0" t="n">
         <v>1</v>
       </c>
+      <c r="I9" s="0" t="n">
+        <f aca="false">0.67</f>
+        <v>0.67</v>
+      </c>
+      <c r="J9" s="0" t="n">
+        <f aca="false">25/30</f>
+        <v>0.833333333333333</v>
+      </c>
       <c r="K9" s="0" t="n">
         <f aca="false">26.5/30</f>
         <v>0.883333333333333</v>
@@ -408,13 +486,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F10" s="0" t="n">
         <f aca="false">14/17</f>
@@ -424,6 +502,14 @@
         <v>0</v>
       </c>
       <c r="H10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="0" t="n">
+        <f aca="false">0</f>
         <v>0</v>
       </c>
       <c r="K10" s="0" t="n">

--- a/Grades/Grades.xlsx
+++ b/Grades/Grades.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
   <si>
     <t xml:space="preserve">First name</t>
   </si>
@@ -50,6 +50,9 @@
   </si>
   <si>
     <t xml:space="preserve">Final Project Proposal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homework 6</t>
   </si>
   <si>
     <t xml:space="preserve">Luka</t>
@@ -217,8 +220,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L11"/>
-  <sheetFormatPr defaultColWidth="8.5234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultColWidth="8.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.3"/>
@@ -227,6 +230,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="11.3"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -265,16 +269,19 @@
       <c r="L2" s="0" t="s">
         <v>9</v>
       </c>
+      <c r="M2" s="0" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F3" s="0" t="n">
         <f aca="false">12.5/17</f>
@@ -298,16 +305,22 @@
         <f aca="false">21/30</f>
         <v>0.7</v>
       </c>
+      <c r="L3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" s="0" t="n">
         <f aca="false">16/17</f>
@@ -331,36 +344,43 @@
         <f aca="false">28.5/30</f>
         <v>0.95</v>
       </c>
+      <c r="L4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" s="0" t="n">
+        <f aca="false">9/10</f>
+        <v>0.9</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F5" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F6" s="0" t="n">
         <f aca="false">14/17</f>
@@ -384,16 +404,23 @@
         <f aca="false">27/30</f>
         <v>0.9</v>
       </c>
+      <c r="L6" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="0" t="n">
+        <f aca="false">13/10</f>
+        <v>1.3</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F7" s="0" t="n">
         <f aca="false">11/17</f>
@@ -417,16 +444,23 @@
         <f aca="false">24/30</f>
         <v>0.8</v>
       </c>
+      <c r="L7" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="0" t="n">
+        <f aca="false">13/10</f>
+        <v>1.3</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F8" s="0" t="n">
         <f aca="false">14/17</f>
@@ -450,16 +484,22 @@
         <f aca="false">25.5/30</f>
         <v>0.85</v>
       </c>
+      <c r="L8" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="0" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="0" t="n">
         <f aca="false">15/17</f>
@@ -483,16 +523,23 @@
         <f aca="false">26.5/30</f>
         <v>0.883333333333333</v>
       </c>
+      <c r="L9" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="0" t="n">
+        <f aca="false">10/10</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F10" s="0" t="n">
         <f aca="false">14/17</f>
@@ -515,6 +562,12 @@
       <c r="K10" s="0" t="n">
         <f aca="false">27/30</f>
         <v>0.9</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="0" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Grades/Grades.xlsx
+++ b/Grades/Grades.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
   <si>
     <t xml:space="preserve">First name</t>
   </si>
@@ -53,6 +53,12 @@
   </si>
   <si>
     <t xml:space="preserve">Homework 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Midterm 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Homework 7</t>
   </si>
   <si>
     <t xml:space="preserve">Luka</t>
@@ -220,8 +226,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M11"/>
-  <sheetFormatPr defaultColWidth="8.55078125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:O11"/>
+  <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.3"/>
@@ -231,6 +237,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="11.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11.09"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -272,16 +279,22 @@
       <c r="M2" s="0" t="s">
         <v>10</v>
       </c>
+      <c r="N2" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="O2" s="0" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F3" s="0" t="n">
         <f aca="false">12.5/17</f>
@@ -314,13 +327,13 @@
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F4" s="0" t="n">
         <f aca="false">16/17</f>
@@ -354,33 +367,33 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F5" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F6" s="0" t="n">
         <f aca="false">14/17</f>
@@ -414,13 +427,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F7" s="0" t="n">
         <f aca="false">11/17</f>
@@ -451,16 +464,20 @@
         <f aca="false">13/10</f>
         <v>1.3</v>
       </c>
+      <c r="O7" s="0" t="n">
+        <f aca="false">10/10</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F8" s="0" t="n">
         <f aca="false">14/17</f>
@@ -493,13 +510,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F9" s="0" t="n">
         <f aca="false">15/17</f>
@@ -533,23 +550,23 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F10" s="0" t="n">
         <f aca="false">14/17</f>
         <v>0.823529411764706</v>
       </c>
       <c r="G10" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" s="0" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="0" t="n">
         <f aca="false">0</f>

--- a/Grades/Grades.xlsx
+++ b/Grades/Grades.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
   <si>
     <t xml:space="preserve">First name</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t xml:space="preserve">Homework 7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final Project</t>
   </si>
   <si>
     <t xml:space="preserve">Luka</t>
@@ -226,8 +229,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
-  <sheetFormatPr defaultColWidth="8.5625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:P11"/>
+  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.3"/>
@@ -237,6 +240,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="17.95"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="11.3"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="11.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11.09"/>
   </cols>
   <sheetData>
@@ -285,16 +289,19 @@
       <c r="O2" s="0" t="s">
         <v>12</v>
       </c>
+      <c r="P2" s="0" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F3" s="0" t="n">
         <f aca="false">12.5/17</f>
@@ -304,7 +311,8 @@
         <v>0</v>
       </c>
       <c r="H3" s="0" t="n">
-        <v>0</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="I3" s="0" t="n">
         <f aca="false">1</f>
@@ -322,18 +330,27 @@
         <v>1</v>
       </c>
       <c r="M3" s="0" t="n">
-        <v>0</v>
+        <f aca="false">1</f>
+        <v>1</v>
+      </c>
+      <c r="O3" s="0" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="P3" s="0" t="n">
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F4" s="0" t="n">
         <f aca="false">16/17</f>
@@ -364,36 +381,44 @@
         <f aca="false">9/10</f>
         <v>0.9</v>
       </c>
+      <c r="O4" s="0" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="P4" s="0" t="n">
+        <f aca="false">1</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F5" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" s="0" t="n">
         <f aca="false">14/17</f>
@@ -424,16 +449,24 @@
         <f aca="false">13/10</f>
         <v>1.3</v>
       </c>
+      <c r="O6" s="0" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="P6" s="0" t="n">
+        <f aca="false">1.2</f>
+        <v>1.2</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" s="0" t="n">
         <f aca="false">11/17</f>
@@ -468,16 +501,20 @@
         <f aca="false">10/10</f>
         <v>1</v>
       </c>
+      <c r="P7" s="0" t="n">
+        <f aca="false">1</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8" s="0" t="n">
         <f aca="false">14/17</f>
@@ -505,18 +542,27 @@
         <v>1</v>
       </c>
       <c r="M8" s="0" t="n">
-        <v>0</v>
+        <f aca="false">10/10</f>
+        <v>1</v>
+      </c>
+      <c r="O8" s="0" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="P8" s="0" t="n">
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F9" s="0" t="n">
         <f aca="false">15/17</f>
@@ -547,16 +593,24 @@
         <f aca="false">10/10</f>
         <v>1</v>
       </c>
+      <c r="O9" s="0" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="P9" s="0" t="n">
+        <f aca="false">1</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F10" s="0" t="n">
         <f aca="false">14/17</f>
@@ -585,6 +639,14 @@
       </c>
       <c r="M10" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="O10" s="0" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="P10" s="0" t="n">
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Grades/Grades.xlsx
+++ b/Grades/Grades.xlsx
@@ -230,7 +230,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultColWidth="8.5703125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.3"/>
@@ -242,6 +242,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="11.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="11.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11.09"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10.79"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">

--- a/Grades/Grades.xlsx
+++ b/Grades/Grades.xlsx
@@ -230,7 +230,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultColWidth="8.578125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.3"/>
@@ -334,6 +334,10 @@
         <f aca="false">1</f>
         <v>1</v>
       </c>
+      <c r="N3" s="0" t="n">
+        <f aca="false">33/40</f>
+        <v>0.825</v>
+      </c>
       <c r="O3" s="0" t="n">
         <f aca="false">0</f>
         <v>0</v>
@@ -382,6 +386,10 @@
         <f aca="false">9/10</f>
         <v>0.9</v>
       </c>
+      <c r="N4" s="0" t="n">
+        <f aca="false">35/40</f>
+        <v>0.875</v>
+      </c>
       <c r="O4" s="0" t="n">
         <f aca="false">0</f>
         <v>0</v>
@@ -450,6 +458,10 @@
         <f aca="false">13/10</f>
         <v>1.3</v>
       </c>
+      <c r="N6" s="0" t="n">
+        <f aca="false">31/40</f>
+        <v>0.775</v>
+      </c>
       <c r="O6" s="0" t="n">
         <f aca="false">0</f>
         <v>0</v>
@@ -498,6 +510,10 @@
         <f aca="false">13/10</f>
         <v>1.3</v>
       </c>
+      <c r="N7" s="0" t="n">
+        <f aca="false">33/40</f>
+        <v>0.825</v>
+      </c>
       <c r="O7" s="0" t="n">
         <f aca="false">10/10</f>
         <v>1</v>
@@ -546,6 +562,10 @@
         <f aca="false">10/10</f>
         <v>1</v>
       </c>
+      <c r="N8" s="0" t="n">
+        <f aca="false">36/40</f>
+        <v>0.9</v>
+      </c>
       <c r="O8" s="0" t="n">
         <f aca="false">0</f>
         <v>0</v>
@@ -594,6 +614,10 @@
         <f aca="false">10/10</f>
         <v>1</v>
       </c>
+      <c r="N9" s="0" t="n">
+        <f aca="false">39/40</f>
+        <v>0.975</v>
+      </c>
       <c r="O9" s="0" t="n">
         <f aca="false">0</f>
         <v>0</v>
@@ -640,6 +664,10 @@
       </c>
       <c r="M10" s="0" t="n">
         <v>0</v>
+      </c>
+      <c r="N10" s="0" t="n">
+        <f aca="false">40/40</f>
+        <v>1</v>
       </c>
       <c r="O10" s="0" t="n">
         <f aca="false">0</f>

--- a/Grades/Grades.xlsx
+++ b/Grades/Grades.xlsx
@@ -230,7 +230,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:P11"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11.3"/>
@@ -648,12 +648,12 @@
         <v>1</v>
       </c>
       <c r="I10" s="0" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">1</f>
+        <v>1</v>
       </c>
       <c r="J10" s="0" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
+        <f aca="false">24/30</f>
+        <v>0.8</v>
       </c>
       <c r="K10" s="0" t="n">
         <f aca="false">27/30</f>
@@ -663,7 +663,8 @@
         <v>1</v>
       </c>
       <c r="M10" s="0" t="n">
-        <v>0</v>
+        <f aca="false">10/10</f>
+        <v>1</v>
       </c>
       <c r="N10" s="0" t="n">
         <f aca="false">40/40</f>

--- a/Grades/Grades.xlsx
+++ b/Grades/Grades.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="44">
   <si>
     <t xml:space="preserve">First name</t>
   </si>
@@ -64,6 +64,15 @@
     <t xml:space="preserve">Final Project</t>
   </si>
   <si>
+    <t xml:space="preserve">Raw Final Grade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">w/ Curve</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Letter</t>
+  </si>
+  <si>
     <t xml:space="preserve">Luka</t>
   </si>
   <si>
@@ -73,6 +82,9 @@
     <t xml:space="preserve">tkenderi@poets.whittier.edu</t>
   </si>
   <si>
+    <t xml:space="preserve">B-</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kamarina</t>
   </si>
   <si>
@@ -82,6 +94,9 @@
     <t xml:space="preserve">khewett@poets.whittier.edu</t>
   </si>
   <si>
+    <t xml:space="preserve">A-</t>
+  </si>
+  <si>
     <t xml:space="preserve">--</t>
   </si>
   <si>
@@ -94,6 +109,9 @@
     <t xml:space="preserve">che@poets.whittier.edu</t>
   </si>
   <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
     <t xml:space="preserve">David</t>
   </si>
   <si>
@@ -112,6 +130,9 @@
     <t xml:space="preserve">omartine@poets.whittier.edu</t>
   </si>
   <si>
+    <t xml:space="preserve">B+</t>
+  </si>
+  <si>
     <t xml:space="preserve">Loren</t>
   </si>
   <si>
@@ -128,6 +149,9 @@
   </si>
   <si>
     <t xml:space="preserve">tcarlson@poets.whittier.edu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A+</t>
   </si>
 </sst>
 </file>
@@ -137,7 +161,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -159,6 +183,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -203,12 +235,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -229,7 +265,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:P11"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr defaultColWidth="8.6015625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.39"/>
@@ -243,9 +279,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="11.6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="11.09"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="14.62"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -254,6 +291,13 @@
       </c>
       <c r="C1" s="1" t="s">
         <v>2</v>
+      </c>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -293,16 +337,27 @@
       <c r="P2" s="0" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q2" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="R2" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F3" s="0" t="n">
         <f aca="false">12.5/17</f>
@@ -346,16 +401,33 @@
         <f aca="false">1</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q3" s="0" t="n">
+        <f aca="false">0.3*(F3+G3+H3+I3+J3+M3+O3)/7+MAX(K3,N3)*0.3+MIN(K3,N3)*0.25+0.15*P3</f>
+        <v>0.772584033613445</v>
+      </c>
+      <c r="R3" s="0" t="n">
+        <f aca="false">Q3+0.3/7</f>
+        <v>0.815441176470588</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F4" s="0" t="n">
         <f aca="false">16/17</f>
@@ -398,36 +470,56 @@
         <f aca="false">1</f>
         <v>1</v>
       </c>
+      <c r="Q4" s="0" t="n">
+        <f aca="false">0.3*(F4+G4+H4+I4+J4+M4+O4)/7+MAX(K4,N4)*0.3+MIN(K4,N4)*0.25+0.15*P4</f>
+        <v>0.861228991596639</v>
+      </c>
+      <c r="R4" s="0" t="n">
+        <f aca="false">Q4+0.3/7</f>
+        <v>0.904086134453781</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="F5" s="0" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="G5" s="0" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H5" s="0" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="I5" s="0" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J5" s="0" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="K5" s="0" t="s">
-        <v>20</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F6" s="0" t="n">
         <f aca="false">14/17</f>
@@ -470,16 +562,33 @@
         <f aca="false">1.2</f>
         <v>1.2</v>
       </c>
+      <c r="Q6" s="0" t="n">
+        <f aca="false">0.3*(F6+G6+H6+I6+J6+M6+O6)/7+MAX(K6,N6)*0.3+MIN(K6,N6)*0.25+0.15*P6</f>
+        <v>0.901901260504202</v>
+      </c>
+      <c r="R6" s="0" t="n">
+        <f aca="false">Q6+0.3/7</f>
+        <v>0.944758403361344</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F7" s="0" t="n">
         <f aca="false">11/17</f>
@@ -522,16 +631,33 @@
         <f aca="false">1</f>
         <v>1</v>
       </c>
+      <c r="Q7" s="0" t="n">
+        <f aca="false">0.3*(F7+G7+H7+I7+J7+M7+O7)/7+MAX(K7,N7)*0.3+MIN(K7,N7)*0.25+0.15*P7</f>
+        <v>0.87094537815126</v>
+      </c>
+      <c r="R7" s="0" t="n">
+        <f aca="false">Q7+0.3/7</f>
+        <v>0.913802521008403</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="U7" s="2" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F8" s="0" t="n">
         <f aca="false">14/17</f>
@@ -574,16 +700,33 @@
         <f aca="false">1</f>
         <v>1</v>
       </c>
+      <c r="Q8" s="0" t="n">
+        <f aca="false">0.3*(F8+G8+H8+I8+J8+M8+O8)/7+MAX(K8,N8)*0.3+MIN(K8,N8)*0.25+0.15*P8</f>
+        <v>0.825079831932773</v>
+      </c>
+      <c r="R8" s="0" t="n">
+        <f aca="false">Q8+0.3/7</f>
+        <v>0.867936974789916</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F9" s="0" t="n">
         <f aca="false">15/17</f>
@@ -626,16 +769,33 @@
         <f aca="false">1</f>
         <v>1</v>
       </c>
+      <c r="Q9" s="0" t="n">
+        <f aca="false">0.3*(F9+G9+H9+I9+J9+M9+O9)/7+MAX(K9,N9)*0.3+MIN(K9,N9)*0.25+0.15*P9</f>
+        <v>0.894148459383753</v>
+      </c>
+      <c r="R9" s="0" t="n">
+        <f aca="false">Q9+0.3/7</f>
+        <v>0.937005602240896</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F10" s="0" t="n">
         <f aca="false">14/17</f>
@@ -678,12 +838,36 @@
         <f aca="false">1</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="Q10" s="0" t="n">
+        <f aca="false">0.3*(F10+G10+H10+I10+J10+M10+O10)/7+MAX(K10,N10)*0.3+MIN(K10,N10)*0.25+0.15*P10</f>
+        <v>0.916008403361345</v>
+      </c>
+      <c r="R10" s="0" t="n">
+        <f aca="false">Q10+0.3/7</f>
+        <v>0.958865546218487</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511811023622047" footer="0.511811023622047"/>
